--- a/assets/constructions/examples/ctd_mko_radial_groove.xlsx
+++ b/assets/constructions/examples/ctd_mko_radial_groove.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,11 +594,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7VGSR1.71-1.50GM3VTX</t>
+          <t>11VGSR3.18-3.25GM3 VTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,29 +643,29 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>12.7</v>
+        <v>21.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>5.75</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>0.055</v>
+        <v>0.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.055</v>
+        <v>0.04</v>
       </c>
       <c r="R2" t="n">
-        <v>0.055</v>
+        <v>0.04</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +675,7 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>VARGUS_V:7V</t>
+          <t>VARGUS_V:11V</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -691,13 +716,32 @@
       <c r="AG2" t="inlineStr">
         <is>
           <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>6102.56</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7VGS0.84-1.50GM3VBX</t>
+          <t>11VGS1.17-3.25GM3 VBX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -717,29 +761,29 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>12.7</v>
+        <v>21.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.84</v>
+        <v>1.17</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>5.75</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -749,7 +793,7 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>VARGUS_V:7V</t>
+          <t>VARGUS_V:11V</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -790,13 +834,32 @@
       <c r="AG3" t="inlineStr">
         <is>
           <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>6102.56</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9VGSR3.18-2.50GM3VBX</t>
+          <t>11VGSR2.39-3.25GM3 VTX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,29 +879,29 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>16.7</v>
+        <v>21.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.18</v>
+        <v>2.39</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>4.45</v>
+        <v>5.75</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -848,7 +911,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>VARGUS_V:9V</t>
+          <t>VARGUS_V:11V</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,12 +921,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -889,13 +952,32 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>6102.56</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9VGSR2.39-2.50GM3 VTX</t>
+          <t>7VGS1.21-1.50GM3VTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -915,29 +997,29 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>16.7</v>
+        <v>12.7</v>
       </c>
       <c r="K5" t="n">
-        <v>2.39</v>
+        <v>1.21</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>4.45</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="R5" t="n">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -947,7 +1029,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>VARGUS_V:9V</t>
+          <t>VARGUS_V:7V</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -988,13 +1070,32 @@
       <c r="AG5" t="inlineStr">
         <is>
           <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>3470.5</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9VGR1.10-2.50GM3 VTX</t>
+          <t>11VGSR1.71-3.25GM3 VBX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1002,51 +1103,41 @@
           <t>VARGUS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GM Slot</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9V.. (GM Slot)</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PKNH</t>
-        </is>
-      </c>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>16.7</v>
+        <v>21.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>4.45</v>
+        <v>5.75</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+        <v>3.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.055</v>
+      </c>
       <c r="R6" t="n">
-        <v>1.1</v>
+        <v>0.055</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1056,7 +1147,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>VARGUS_V:9V</t>
+          <t>VARGUS_V:11V</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1066,12 +1157,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1096,7 +1187,26 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2022/Groove Milling Metric Groovex</t>
+          <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>6102.56</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
